--- a/連絡先一覧.xlsx
+++ b/連絡先一覧.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -542,26 +542,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Ryo Kawakami</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Libetee Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>pipopan771@gmail.com</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
